--- a/Field_Elevate_Sector_Monthly_Returns.xlsx
+++ b/Field_Elevate_Sector_Monthly_Returns.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O104"/>
+  <dimension ref="A1:O105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5637,7 +5637,6 @@
           <t>2026-01</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr"/>
       <c r="C104" t="n">
         <v>7.47</v>
       </c>
@@ -5680,6 +5679,57 @@
       </c>
       <c r="O104" t="n">
         <v>2.78</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr"/>
+      <c r="C105" t="n">
+        <v>-0.91</v>
+      </c>
+      <c r="D105" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="E105" t="n">
+        <v>14.42</v>
+      </c>
+      <c r="F105" t="n">
+        <v>-16.72</v>
+      </c>
+      <c r="G105" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="H105" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I105" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="J105" t="n">
+        <v>7.37</v>
+      </c>
+      <c r="K105" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L105" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>Precious Metals</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>Real Assets</t>
+        </is>
+      </c>
+      <c r="O105" t="n">
+        <v>1.67</v>
       </c>
     </row>
   </sheetData>

--- a/Field_Elevate_Sector_Monthly_Returns.xlsx
+++ b/Field_Elevate_Sector_Monthly_Returns.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O105"/>
+  <dimension ref="A1:O106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5687,7 +5687,6 @@
           <t>2026-02</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr"/>
       <c r="C105" t="n">
         <v>-0.91</v>
       </c>
@@ -5730,6 +5729,57 @@
       </c>
       <c r="O105" t="n">
         <v>1.67</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr"/>
+      <c r="C106" t="n">
+        <v>-5.38</v>
+      </c>
+      <c r="D106" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="E106" t="n">
+        <v>-14.94</v>
+      </c>
+      <c r="F106" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="G106" t="n">
+        <v>-1.95</v>
+      </c>
+      <c r="H106" t="n">
+        <v>-7.3</v>
+      </c>
+      <c r="I106" t="n">
+        <v>-4.75</v>
+      </c>
+      <c r="J106" t="n">
+        <v>-5.06</v>
+      </c>
+      <c r="K106" t="n">
+        <v>5</v>
+      </c>
+      <c r="L106" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>Crypto &amp; Digital Assets</t>
+        </is>
+      </c>
+      <c r="O106" t="n">
+        <v>-2.97</v>
       </c>
     </row>
   </sheetData>

--- a/Field_Elevate_Sector_Monthly_Returns.xlsx
+++ b/Field_Elevate_Sector_Monthly_Returns.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O106"/>
+  <dimension ref="A1:O107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5737,7 +5737,6 @@
           <t>2026-03</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr"/>
       <c r="C106" t="n">
         <v>-5.38</v>
       </c>
@@ -5780,6 +5779,57 @@
       </c>
       <c r="O106" t="n">
         <v>-2.97</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr"/>
+      <c r="C107" t="n">
+        <v>30.21</v>
+      </c>
+      <c r="D107" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="E107" t="n">
+        <v>-2.44</v>
+      </c>
+      <c r="F107" t="n">
+        <v>9.98</v>
+      </c>
+      <c r="G107" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H107" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="I107" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="J107" t="n">
+        <v>6</v>
+      </c>
+      <c r="K107" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="L107" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>Tech &amp; Innovation</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>Crypto &amp; Digital Assets</t>
+        </is>
+      </c>
+      <c r="O107" t="n">
+        <v>5.75</v>
       </c>
     </row>
   </sheetData>

--- a/Field_Elevate_Sector_Monthly_Returns.xlsx
+++ b/Field_Elevate_Sector_Monthly_Returns.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O107"/>
+  <dimension ref="A1:O108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5787,7 +5787,6 @@
           <t>2026-04</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr"/>
       <c r="C107" t="n">
         <v>30.21</v>
       </c>
@@ -5830,6 +5829,57 @@
       </c>
       <c r="O107" t="n">
         <v>5.75</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr"/>
+      <c r="C108" t="n">
+        <v>21.54</v>
+      </c>
+      <c r="D108" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="E108" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="F108" t="n">
+        <v>-6.61</v>
+      </c>
+      <c r="G108" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H108" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="I108" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="J108" t="n">
+        <v>-2.47</v>
+      </c>
+      <c r="K108" t="n">
+        <v>-2.78</v>
+      </c>
+      <c r="L108" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>Tech &amp; Innovation</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>Health &amp; Biotech</t>
+        </is>
+      </c>
+      <c r="O108" t="n">
+        <v>1.34</v>
       </c>
     </row>
   </sheetData>

--- a/Field_Elevate_Sector_Monthly_Returns.xlsx
+++ b/Field_Elevate_Sector_Monthly_Returns.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O108"/>
+  <dimension ref="A1:O109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5837,7 +5837,6 @@
           <t>2026-05</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr"/>
       <c r="C108" t="n">
         <v>21.54</v>
       </c>
@@ -5880,6 +5879,57 @@
       </c>
       <c r="O108" t="n">
         <v>1.34</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr"/>
+      <c r="C109" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="D109" t="n">
+        <v>-9.75</v>
+      </c>
+      <c r="E109" t="n">
+        <v>-13.29</v>
+      </c>
+      <c r="F109" t="n">
+        <v>-20.92</v>
+      </c>
+      <c r="G109" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H109" t="n">
+        <v>-1.31</v>
+      </c>
+      <c r="I109" t="n">
+        <v>10.32</v>
+      </c>
+      <c r="J109" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="K109" t="n">
+        <v>-2.13</v>
+      </c>
+      <c r="L109" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>Health &amp; Biotech</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>Tech &amp; Innovation</t>
+        </is>
+      </c>
+      <c r="O109" t="n">
+        <v>-2.82</v>
       </c>
     </row>
   </sheetData>
